--- a/data/dados_cdi.xlsx
+++ b/data/dados_cdi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos_Python\kpis_carteira\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos_Python\kpis_carteira\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60A5C9E-BF5A-4298-8C67-984F5A425A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F00C8E-F0C7-4C11-902D-3243C3559E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCFFE824-CB78-4C25-B1FC-6D08347FDADD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t>Data</t>
   </si>
@@ -1479,9 +1479,6 @@
   </si>
   <si>
     <t>2026.01</t>
-  </si>
-  <si>
-    <t>2026.02</t>
   </si>
   <si>
     <t>Taxa CDI acumulada no mês</t>
@@ -1882,12 +1879,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B448730-148B-4EB8-AA21-D28D0D24EE67}">
-  <dimension ref="A1:G481"/>
+  <dimension ref="A1:G486"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1895,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5731,13 +5729,8 @@
       </c>
       <c r="G480" s="3"/>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A481" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B481" s="1">
-        <v>0.22</v>
-      </c>
+    <row r="486" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C486" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/dados_cdi.xlsx
+++ b/data/dados_cdi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos_Python\kpis_carteira\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F00C8E-F0C7-4C11-902D-3243C3559E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890D96BA-4A9F-453A-B6D4-838B18652A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BCFFE824-CB78-4C25-B1FC-6D08347FDADD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t>Data</t>
   </si>
@@ -1482,6 +1482,9 @@
   </si>
   <si>
     <t>Taxa CDI acumulada no mês</t>
+  </si>
+  <si>
+    <t>2026.02</t>
   </si>
 </sst>
 </file>
@@ -5729,7 +5732,15 @@
       </c>
       <c r="G480" s="3"/>
     </row>
-    <row r="486" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B481" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C486" s="3"/>
     </row>
   </sheetData>
